--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:19:25+00:00</t>
+    <t>2026-09-30T09:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -122,7 +122,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://bih-cei.github.io/PCOR-MII/CodeSystem/dem-einkommen|0.1.0</t>
+    <t>https://bih-cei.github.io/PCOR-MII/CodeSystem/dem-einkommen|0.3.0</t>
   </si>
   <si>
     <t>Level</t>
@@ -152,7 +152,7 @@
     <t>band-niedrig</t>
   </si>
   <si>
-    <t>Bis zu 2.300 € pro Monat</t>
+    <t>Up to €2,300 a month</t>
   </si>
   <si>
     <t>false</t>
@@ -161,25 +161,25 @@
     <t>band-mittel</t>
   </si>
   <si>
-    <t>Zwischen 2.300 € und 5.200 € pro Monat</t>
+    <t>Between €2,300 and €5,200 a month</t>
   </si>
   <si>
     <t>band-hoch</t>
   </si>
   <si>
-    <t>5.200 € pro Monat oder mehr</t>
+    <t>€5,200 a month or more</t>
   </si>
   <si>
     <t>weiss-nicht</t>
   </si>
   <si>
-    <t>Ich weiss es nicht</t>
+    <t>Don't know</t>
   </si>
   <si>
     <t>keine-angabe</t>
   </si>
   <si>
-    <t>Möchte ich nicht sagen</t>
+    <t>Prefer not to say</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:40:42+00:00</t>
+    <t>2026-09-30T19:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:42:59+00:00</t>
+    <t>2026-09-30T19:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:54:40+00:00</t>
+    <t>2026-10-01T09:59:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T09:59:00+00:00</t>
+    <t>2026-10-01T11:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:16:03+00:00</t>
+    <t>2026-10-01T11:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:25:55+00:00</t>
+    <t>2026-10-01T11:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:30:23+00:00</t>
+    <t>2026-10-01T13:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:09:50+00:00</t>
+    <t>2026-10-01T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:39:45+00:00</t>
+    <t>2026-10-01T14:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:59:54+00:00</t>
+    <t>2026-10-13T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T13:38:01+00:00</t>
+    <t>2026-10-13T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-einkommen-vs.xlsx
+++ b/ValueSet-dem-einkommen-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
